--- a/ADP/python_packages_full_list.xlsx
+++ b/ADP/python_packages_full_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_00_TOY\kaggle\ADP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3BE75E40-B4C2-42CC-8400-B5D86ECE5C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{166358C3-0D3B-410A-B03C-7440D2AFAD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4BA5C335-1294-48CF-8971-F2484C759167}"/>
   </bookViews>
@@ -11489,32 +11489,17 @@
       </c>
     </row>
     <row r="73" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="I73" t="s">
-        <v>148</v>
-      </c>
-      <c r="J73" t="s">
-        <v>148</v>
-      </c>
-      <c r="K73" t="s">
-        <v>148</v>
-      </c>
-      <c r="L73" t="s">
-        <v>148</v>
-      </c>
-      <c r="M73" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="74" spans="5:13" x14ac:dyDescent="0.3">
@@ -11531,19 +11516,19 @@
         <v>148</v>
       </c>
       <c r="I74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="5:13" x14ac:dyDescent="0.3">
@@ -11559,6 +11544,21 @@
       <c r="H75" t="s">
         <v>149</v>
       </c>
+      <c r="I75" t="s">
+        <v>149</v>
+      </c>
+      <c r="J75" t="s">
+        <v>149</v>
+      </c>
+      <c r="K75" t="s">
+        <v>149</v>
+      </c>
+      <c r="L75" t="s">
+        <v>149</v>
+      </c>
+      <c r="M75" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="76" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E76" t="s">
@@ -11793,16 +11793,16 @@
       </c>
     </row>
     <row r="84" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -12387,16 +12387,16 @@
       </c>
     </row>
     <row r="105" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G105" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="1" t="s">
         <v>200</v>
       </c>
     </row>
@@ -13329,28 +13329,28 @@
       </c>
     </row>
     <row r="138" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E138" t="s">
+      <c r="E138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="I138" t="s">
+      <c r="I138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="J138" t="s">
+      <c r="J138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="K138" t="s">
+      <c r="K138" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="L138" t="s">
+      <c r="L138" s="1" t="s">
         <v>250</v>
       </c>
     </row>
